--- a/data_qa/data_qa_dashboard.xlsx
+++ b/data_qa/data_qa_dashboard.xlsx
@@ -8,23 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\SaaS_Product_Analysis_Based_on_Customer_Feedback_and_Competitor_Performance\data_qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D2A5B1-5025-4CA2-9C29-6E273A6FDEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA364FA3-8E22-40CB-BE8E-D6799079FF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Meet Validation" sheetId="1" r:id="rId1"/>
-    <sheet name="Teams Validation" sheetId="2" r:id="rId2"/>
-    <sheet name="Webex Validation" sheetId="3" r:id="rId3"/>
-    <sheet name="Zoom Validation" sheetId="4" r:id="rId4"/>
-    <sheet name="Issues Reduced" sheetId="9" r:id="rId5"/>
-    <sheet name="Overall Completeness" sheetId="11" r:id="rId6"/>
-    <sheet name="Overall Validity" sheetId="6" r:id="rId7"/>
-    <sheet name="Overall Uniqueness" sheetId="7" r:id="rId8"/>
-    <sheet name="Overall Issues Reductions" sheetId="8" r:id="rId9"/>
+    <sheet name="DATA Quality" sheetId="1" r:id="rId1"/>
+    <sheet name="Issues Reduced" sheetId="9" r:id="rId2"/>
+    <sheet name="PT_Data_Quality" sheetId="13" r:id="rId3"/>
+    <sheet name="PT_Issues" sheetId="14" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_product">#N/A</definedName>
+    <definedName name="Slicer_product1">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
+  <pivotCaches>
+    <pivotCache cacheId="19" r:id="rId5"/>
+    <pivotCache cacheId="23" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId8"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -33,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>rows_before_clean</t>
   </si>
@@ -62,15 +74,6 @@
     <t>Zoom</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Total Issues</t>
-  </si>
-  <si>
-    <t>Reduced Issues</t>
-  </si>
-  <si>
     <t>Teams</t>
   </si>
   <si>
@@ -80,10 +83,52 @@
     <t>Webex</t>
   </si>
   <si>
-    <t>Issues Dif</t>
-  </si>
-  <si>
-    <t>Issues Reduction(%)</t>
+    <t>product</t>
+  </si>
+  <si>
+    <t>total_issues</t>
+  </si>
+  <si>
+    <t>reduced_Issues</t>
+  </si>
+  <si>
+    <t>issues_dif</t>
+  </si>
+  <si>
+    <t>issues_reduction(%)</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>Average of completeness</t>
+  </si>
+  <si>
+    <t>Average of uniqueness</t>
+  </si>
+  <si>
+    <t>Average of validity</t>
+  </si>
+  <si>
+    <t>Average of row_retention</t>
+  </si>
+  <si>
+    <t>Sum of total_issues</t>
+  </si>
+  <si>
+    <t>Sum of reduced_Issues</t>
+  </si>
+  <si>
+    <t>Sum of issues_dif</t>
   </si>
 </sst>
 </file>
@@ -91,7 +136,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -104,21 +149,33 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -126,22 +183,185 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="37">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -152,6 +372,592 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>91441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1127760</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="product 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{874A9D3E-1EF1-9F32-E015-026BC033B509}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="product 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7901940" y="91441"/>
+              <a:ext cx="1828800" cy="1554480"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>861060</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>137159</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="product">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB1CE87-86DF-3F0C-7582-ADC050E2330D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="product"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5273040" y="45720"/>
+              <a:ext cx="1470660" cy="1554479"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ujjwal Karki" refreshedDate="46267.4624744213" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="4" xr:uid="{91162948-C8C1-46E1-B0F3-E8B7DEEDA32F}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table12"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="product" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Meet"/>
+        <s v="Teams"/>
+        <s v="Webex"/>
+        <s v="Zoom"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="rows_before_clean" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="6000" maxValue="6000"/>
+    </cacheField>
+    <cacheField name="rows_after_clean" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5999" maxValue="6000"/>
+    </cacheField>
+    <cacheField name="rows_rem" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="duplicate_reduc" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="completeness" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.92879999999999996" maxValue="0.98599999999999999"/>
+    </cacheField>
+    <cacheField name="uniqueness" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="validity" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="row_retention" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.99983333333333302" maxValue="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1658260399"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ujjwal Karki" refreshedDate="46267.492475694446" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="4" xr:uid="{A87839A3-35E0-4805-9B72-00CA17474206}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table11"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="product" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Zoom"/>
+        <s v="Teams"/>
+        <s v="Meet"/>
+        <s v="Webex"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="total_issues" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="4"/>
+    </cacheField>
+    <cacheField name="reduced_Issues" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="3"/>
+    </cacheField>
+    <cacheField name="issues_dif" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="issues_reduction(%)" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.75" maxValue="0.75"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="715696115"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="4">
+  <r>
+    <x v="0"/>
+    <n v="6000"/>
+    <n v="6000"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.98599999999999999"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="6000"/>
+    <n v="5999"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0.96739456576095995"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0.99983333333333302"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="6000"/>
+    <n v="6000"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.97130000000000005"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="6000"/>
+    <n v="6000"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0.92879999999999996"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="4">
+  <r>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0.75"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0.75"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0.75"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0.75"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99E53967-C66C-4D23-983E-103C5664C688}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:E6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Average of completeness" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Average of uniqueness" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Average of validity" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Average of row_retention" fld="8" subtotal="average" baseField="0" baseItem="1" numFmtId="164"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="28">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea field="0" grandRow="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2210FF8F-50C3-47D8-AAA9-A90829F54A80}" name="PivotTable2" cacheId="23" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:F5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of total_issues" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Sum of reduced_Issues" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of issues_dif" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_product" xr10:uid="{75E81686-A296-44B7-9DF5-D036041AD7D5}" sourceName="product">
+  <pivotTables>
+    <pivotTable tabId="14" name="PivotTable2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="715696115">
+      <items count="4">
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="3" s="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_product1" xr10:uid="{8F299F2E-25D6-4028-823B-2AEB9A6D85B9}" sourceName="product">
+  <pivotTables>
+    <pivotTable tabId="13" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1658260399">
+      <items count="4">
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="product 1" xr10:uid="{7B05AFE0-5CFC-4474-99E8-5BB65232B90B}" cache="Slicer_product1" caption="product" rowHeight="234950"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="product" xr10:uid="{B8400369-724B-4321-BC3B-DFCB5A45C9C9}" cache="Slicer_product" caption="product" rowHeight="234950"/>
+</slicers>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{70C641C8-E17E-4864-A823-6B0B044CD8B5}" name="Table12" displayName="Table12" ref="A1:I5" totalsRowShown="0" headerRowDxfId="34">
+  <autoFilter ref="A1:I5" xr:uid="{70C641C8-E17E-4864-A823-6B0B044CD8B5}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{255300D9-3B20-431D-92A4-8B311AD093A8}" name="product"/>
+    <tableColumn id="2" xr3:uid="{1E1DD67E-68DF-4F75-8435-58AC8C42AE91}" name="rows_before_clean"/>
+    <tableColumn id="3" xr3:uid="{FBAC98E4-EA90-4EAC-A80A-E32FDF7EA0AD}" name="rows_after_clean"/>
+    <tableColumn id="4" xr3:uid="{11C01F73-3E61-4548-A510-65CFAD2FF90B}" name="rows_rem"/>
+    <tableColumn id="5" xr3:uid="{753D29EC-821F-40AB-B735-4B3FCED9CADD}" name="duplicate_reduc"/>
+    <tableColumn id="6" xr3:uid="{3F5A9B95-36D4-4616-AC92-DEA610463961}" name="completeness" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{1CE922A8-6811-48B4-9E93-3FAC2FD37210}" name="uniqueness" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{D58DDBD3-2367-4CC0-8247-ECAFD598FE93}" name="validity" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{1F8FFAEA-9B12-4F92-987B-D71CE2BFA92E}" name="row_retention" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1A00F067-74BA-4473-9B90-26CC17089166}" name="Table11" displayName="Table11" ref="A1:E5" totalsRowShown="0" headerRowDxfId="35" tableBorderDxfId="36">
+  <autoFilter ref="A1:E5" xr:uid="{1A00F067-74BA-4473-9B90-26CC17089166}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{3DAF244A-F962-4411-8473-4EC00494B072}" name="product"/>
+    <tableColumn id="2" xr3:uid="{D5871DA8-3458-4210-9131-0BC9DA973561}" name="total_issues"/>
+    <tableColumn id="3" xr3:uid="{2F2441AF-EA1A-4982-B12F-D746A1D93F32}" name="reduced_Issues"/>
+    <tableColumn id="4" xr3:uid="{5C2C2D4B-6B84-4806-AA92-BE7194895534}" name="issues_dif">
+      <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{83B53BAE-BA42-4EDA-AAF3-D936855D165B}" name="issues_reduction(%)">
+      <calculatedColumnFormula>(C2/B2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,331 +1223,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>6000</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
       </c>
       <c r="B2">
         <v>6000</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>0.98599999999999999</v>
       </c>
-      <c r="F2" s="3">
-        <v>0.567500358422939</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.1</v>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>6000</v>
+      </c>
+      <c r="C3">
+        <v>5999</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.96739456576095995</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.99983333333333302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>6000</v>
+      </c>
+      <c r="C4">
+        <v>6000</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.97130000000000005</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>6000</v>
+      </c>
+      <c r="C5">
+        <v>6000</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.92879999999999996</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85C08F5-6C81-411D-ADFD-A5353E715D86}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>6000</v>
-      </c>
-      <c r="B2">
-        <v>5999</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.96739456576095995</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.560231803886586</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.99983333333333302</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456B0E81-789A-4B98-A4D6-FCFCA7CF5922}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>6000</v>
-      </c>
-      <c r="B2">
-        <v>6000</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.97130000000000005</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.52875672309787902</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4696CCD4-779A-4D52-B297-8CE8B15EBFB3}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>6000</v>
-      </c>
-      <c r="B2">
-        <v>6000</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.92879999999999996</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.55027784679088998</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2052981-935E-4488-9A58-CA16517C1842}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="4" t="str">
+        <f>'DATA Quality'!A5</f>
+        <v>Zoom</v>
+      </c>
+      <c r="B2" s="4">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <f>B2-C2</f>
         <v>1</v>
       </c>
@@ -751,35 +1440,37 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="6" t="str">
+        <f>'DATA Quality'!A3</f>
+        <v>Teams</v>
+      </c>
+      <c r="B3" s="6">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>3</v>
       </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D6" si="0">B3-C3</f>
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D5" si="0">B3-C3</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E5" si="1">(C3/B3)</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="4" t="str">
+        <f>'DATA Quality'!A2</f>
+        <v>Meet</v>
+      </c>
+      <c r="B4" s="4">
         <v>4</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -789,61 +1480,277 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="6" t="str">
+        <f>'DATA Quality'!A4</f>
+        <v>Webex</v>
+      </c>
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="6">
         <v>3</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="9">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84991F7-A008-48BA-8E95-0BBBD5CEC3D1}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF72164-C490-4B00-83BF-98EC204F41A2}">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.96739456576095995</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.99983333333333302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.97130000000000005</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.92879999999999996</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.96337364144023996</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.99995833333333328</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951FAFF7-073E-498F-BE78-C16A390B1072}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BDC6E5-A7F0-4F7E-B40C-147F107EE830}">
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05572AAA-3C34-45E0-A708-9BE374E8C630}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F971E7-FED2-4F40-9A7E-B5905928CAF8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/data_qa/data_qa_dashboard.xlsx
+++ b/data_qa/data_qa_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\SaaS_Product_Analysis_Based_on_Customer_Feedback_and_Competitor_Performance\data_qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96380B5-F412-4216-9D7E-EFD1632D2E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D29DC5-2759-4705-8519-05A9D9BDA2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
